--- a/data/trans_orig/IP2003-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP2003-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8536</t>
+          <t>8552</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19547</t>
+          <t>19942</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9058</t>
+          <t>8740</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20093</t>
+          <t>19615</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>19994</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>35869</t>
+          <t>35257</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>18,75%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>76841</t>
+          <t>76446</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>87852</t>
+          <t>87836</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>79,72%</t>
+          <t>79,31%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,14%</t>
+          <t>91,13%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>71568</t>
+          <t>72046</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>82603</t>
+          <t>82921</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>78,08%</t>
+          <t>78,6%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,12%</t>
+          <t>90,47%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>152180</t>
+          <t>152792</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>167928</t>
+          <t>168055</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>80,93%</t>
+          <t>81,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,3%</t>
+          <t>89,37%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5333</t>
+          <t>4969</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15629</t>
+          <t>14304</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5014</t>
+          <t>4837</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14227</t>
+          <t>14509</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12245</t>
+          <t>12413</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>25948</t>
+          <t>26121</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>15,93%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>65950</t>
+          <t>67275</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>76246</t>
+          <t>76610</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>80,84%</t>
+          <t>82,47%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,46%</t>
+          <t>93,91%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>68158</t>
+          <t>67876</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>77371</t>
+          <t>77548</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,73%</t>
+          <t>82,39%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>94,13%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>138016</t>
+          <t>137843</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>151719</t>
+          <t>151551</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,17%</t>
+          <t>84,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>92,43%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4822</t>
+          <t>5085</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13478</t>
+          <t>13222</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8812</t>
+          <t>8933</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20368</t>
+          <t>19955</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>15732</t>
+          <t>15589</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>29743</t>
+          <t>29870</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>18,38%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>51199</t>
+          <t>51455</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>59855</t>
+          <t>59592</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>79,16%</t>
+          <t>79,56%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,54%</t>
+          <t>92,14%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>77453</t>
+          <t>77866</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>89009</t>
+          <t>88888</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>79,18%</t>
+          <t>79,6%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,99%</t>
+          <t>90,87%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>132754</t>
+          <t>132627</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>146765</t>
+          <t>146908</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>81,7%</t>
+          <t>81,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,32%</t>
+          <t>90,41%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>22190</t>
+          <t>21302</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>37923</t>
+          <t>37824</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>20082</t>
+          <t>20353</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>36302</t>
+          <t>36370</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>46718</t>
+          <t>45197</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>68992</t>
+          <t>67506</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>17,73%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>153741</t>
+          <t>153840</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>169474</t>
+          <t>170362</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,21%</t>
+          <t>80,27%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,42%</t>
+          <t>88,89%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>152723</t>
+          <t>152655</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>168943</t>
+          <t>168672</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,8%</t>
+          <t>80,76%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,38%</t>
+          <t>89,23%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>311697</t>
+          <t>313183</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>333971</t>
+          <t>335492</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,88%</t>
+          <t>82,27%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,73%</t>
+          <t>88,13%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>18308</t>
+          <t>19181</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>33443</t>
+          <t>33177</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>33,39%</t>
+          <t>33,12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>15655</t>
+          <t>14930</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>29299</t>
+          <t>28316</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>38084</t>
+          <t>37713</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>56509</t>
+          <t>56691</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>25,56%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>66728</t>
+          <t>66994</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>81863</t>
+          <t>80990</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>66,61%</t>
+          <t>66,88%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>81,72%</t>
+          <t>80,85%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>92321</t>
+          <t>93304</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>105965</t>
+          <t>106690</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>75,91%</t>
+          <t>76,72%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>87,13%</t>
+          <t>87,72%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>165283</t>
+          <t>165101</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>183708</t>
+          <t>184079</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>74,52%</t>
+          <t>74,44%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>82,83%</t>
+          <t>83,0%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8644</t>
+          <t>8964</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19801</t>
+          <t>19480</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1302</t>
+          <t>1313</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7253</t>
+          <t>7903</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>12055</t>
+          <t>12047</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>24780</t>
+          <t>24633</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>17,95%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>51727</t>
+          <t>52048</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>62884</t>
+          <t>62564</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>72,32%</t>
+          <t>72,77%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>87,92%</t>
+          <t>87,47%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>58476</t>
+          <t>57826</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>64427</t>
+          <t>64416</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>88,96%</t>
+          <t>87,98%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>112477</t>
+          <t>112624</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>125202</t>
+          <t>125210</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>81,95%</t>
+          <t>82,05%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>84470</t>
+          <t>85011</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>115104</t>
+          <t>114520</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>75476</t>
+          <t>76129</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>104569</t>
+          <t>102688</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>168876</t>
+          <t>167929</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>208258</t>
+          <t>208235</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>490903</t>
+          <t>491487</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>521537</t>
+          <t>520996</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>81,01%</t>
+          <t>81,1%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>86,06%</t>
+          <t>85,97%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>543671</t>
+          <t>545552</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>572764</t>
+          <t>572111</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>83,87%</t>
+          <t>84,16%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>88,36%</t>
+          <t>88,26%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1045989</t>
+          <t>1046012</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1085371</t>
+          <t>1086318</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2994,7 +2994,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>86,54%</t>
+          <t>86,61%</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10823</t>
+          <t>10233</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23795</t>
+          <t>22881</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>28,55%</t>
+          <t>27,46%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3942</t>
+          <t>3798</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12311</t>
+          <t>12459</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>17191</t>
+          <t>16815</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>31878</t>
+          <t>31728</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>19,12%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>59538</t>
+          <t>60452</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>72510</t>
+          <t>73100</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>71,45%</t>
+          <t>72,54%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>87,01%</t>
+          <t>87,72%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>70329</t>
+          <t>70181</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>78698</t>
+          <t>78842</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,1%</t>
+          <t>84,92%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>134096</t>
+          <t>134246</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>148783</t>
+          <t>149159</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>80,79%</t>
+          <t>80,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,64%</t>
+          <t>89,87%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8751</t>
+          <t>9284</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20437</t>
+          <t>21348</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>24,61%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5315</t>
+          <t>5583</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15725</t>
+          <t>15469</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>16794</t>
+          <t>17196</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>31673</t>
+          <t>31940</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>17,86%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>66309</t>
+          <t>65398</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>77995</t>
+          <t>77462</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>76,44%</t>
+          <t>75,39%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,91%</t>
+          <t>89,3%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>76349</t>
+          <t>76605</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>86759</t>
+          <t>86491</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,92%</t>
+          <t>83,2%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>93,94%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>147147</t>
+          <t>146880</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>162026</t>
+          <t>161624</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>82,29%</t>
+          <t>82,14%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,61%</t>
+          <t>90,38%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9489</t>
+          <t>9609</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20537</t>
+          <t>21290</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>26,2%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6972</t>
+          <t>6838</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17306</t>
+          <t>17040</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>19405</t>
+          <t>18731</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>34973</t>
+          <t>34339</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>21,0%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>60712</t>
+          <t>59959</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>71760</t>
+          <t>71640</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>74,72%</t>
+          <t>73,8%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>88,32%</t>
+          <t>88,17%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>64954</t>
+          <t>65220</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>75288</t>
+          <t>75422</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>78,96%</t>
+          <t>79,28%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,52%</t>
+          <t>91,69%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>128535</t>
+          <t>129169</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>144103</t>
+          <t>144777</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>78,61%</t>
+          <t>79,0%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>88,13%</t>
+          <t>88,54%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19653</t>
+          <t>19555</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>35992</t>
+          <t>35249</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18921</t>
+          <t>19048</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>34436</t>
+          <t>33150</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>42557</t>
+          <t>42064</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>64702</t>
+          <t>64691</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>16,13%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>154353</t>
+          <t>155096</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>170692</t>
+          <t>170790</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,09%</t>
+          <t>81,48%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,68%</t>
+          <t>89,73%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>176186</t>
+          <t>177472</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>191701</t>
+          <t>191574</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,65%</t>
+          <t>84,26%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,02%</t>
+          <t>90,96%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>336265</t>
+          <t>336276</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>358410</t>
+          <t>358903</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,86%</t>
+          <t>83,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,39%</t>
+          <t>89,51%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>19561</t>
+          <t>19448</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>34595</t>
+          <t>35716</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>25,79%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>15071</t>
+          <t>15397</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>29526</t>
+          <t>29398</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>39516</t>
+          <t>38682</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>59414</t>
+          <t>59431</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>22,01%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>103877</t>
+          <t>102756</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>118911</t>
+          <t>119024</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>75,02%</t>
+          <t>74,21%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>85,87%</t>
+          <t>85,96%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>102055</t>
+          <t>102183</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>116510</t>
+          <t>116184</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>77,56%</t>
+          <t>77,66%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>88,55%</t>
+          <t>88,3%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>210639</t>
+          <t>210622</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>230537</t>
+          <t>231371</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>78,0%</t>
+          <t>77,99%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>85,37%</t>
+          <t>85,68%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3402</t>
+          <t>3247</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10911</t>
+          <t>11246</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7151</t>
+          <t>7544</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>17062</t>
+          <t>17874</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>26,03%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>13070</t>
+          <t>12845</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>25522</t>
+          <t>25188</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>21,24%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>38988</t>
+          <t>38653</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>46497</t>
+          <t>46652</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>78,13%</t>
+          <t>77,46%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>51602</t>
+          <t>50790</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>61513</t>
+          <t>61120</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>75,15%</t>
+          <t>73,97%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>89,59%</t>
+          <t>89,01%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>93041</t>
+          <t>93375</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>105493</t>
+          <t>105718</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>78,47%</t>
+          <t>78,76%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>88,98%</t>
+          <t>89,17%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>90892</t>
+          <t>90882</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>122054</t>
+          <t>122061</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,7 +5441,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>74191</t>
+          <t>73357</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>102489</t>
+          <t>102622</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>172629</t>
+          <t>172768</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>213536</t>
+          <t>216285</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>16,66%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>507990</t>
+          <t>507983</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>539152</t>
+          <t>539162</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5559,7 +5559,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>85,57%</t>
+          <t>85,58%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>565352</t>
+          <t>565219</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>593650</t>
+          <t>594484</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>84,65%</t>
+          <t>84,63%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>88,89%</t>
+          <t>89,02%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1084349</t>
+          <t>1081600</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1125256</t>
+          <t>1125117</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>83,55%</t>
+          <t>83,34%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>86,7%</t>
+          <t>86,69%</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7515</t>
+          <t>7258</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19277</t>
+          <t>19064</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>24,68%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8451</t>
+          <t>8717</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19799</t>
+          <t>20347</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>19248</t>
+          <t>19366</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>35285</t>
+          <t>34982</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>20,9%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>57977</t>
+          <t>58190</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>69739</t>
+          <t>69996</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>75,05%</t>
+          <t>75,32%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,27%</t>
+          <t>90,6%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>70347</t>
+          <t>69799</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>81695</t>
+          <t>81429</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>78,04%</t>
+          <t>77,43%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,63%</t>
+          <t>90,33%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>132116</t>
+          <t>132419</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>148153</t>
+          <t>148035</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>78,92%</t>
+          <t>79,1%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,5%</t>
+          <t>88,43%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5685</t>
+          <t>5821</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15805</t>
+          <t>15854</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5117</t>
+          <t>4911</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15365</t>
+          <t>14476</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12296</t>
+          <t>12255</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>27488</t>
+          <t>25599</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>12,6%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>81866</t>
+          <t>81817</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>91986</t>
+          <t>91850</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,82%</t>
+          <t>83,77%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>90162</t>
+          <t>91051</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>100410</t>
+          <t>100616</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,44%</t>
+          <t>86,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>175710</t>
+          <t>177599</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>190902</t>
+          <t>190943</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,47%</t>
+          <t>87,4%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>93,97%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2541</t>
+          <t>2599</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10484</t>
+          <t>10316</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2971</t>
+          <t>3432</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11602</t>
+          <t>12506</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6932</t>
+          <t>7360</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>18271</t>
+          <t>18426</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>14,34%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>47229</t>
+          <t>47397</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>55172</t>
+          <t>55114</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>81,83%</t>
+          <t>82,12%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>59207</t>
+          <t>58303</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>67838</t>
+          <t>67377</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,61%</t>
+          <t>82,34%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,15%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>110251</t>
+          <t>110096</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>121590</t>
+          <t>121162</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>85,78%</t>
+          <t>85,66%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>94,27%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>22775</t>
+          <t>21630</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>38865</t>
+          <t>39251</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>20551</t>
+          <t>20024</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>36680</t>
+          <t>36875</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>46337</t>
+          <t>46143</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>69920</t>
+          <t>68295</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>16,62%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>168900</t>
+          <t>168514</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>184990</t>
+          <t>186135</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,29%</t>
+          <t>81,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,04%</t>
+          <t>89,59%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>166455</t>
+          <t>166260</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>182584</t>
+          <t>183111</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,94%</t>
+          <t>81,85%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,88%</t>
+          <t>90,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>340980</t>
+          <t>342605</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>364563</t>
+          <t>364757</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,98%</t>
+          <t>83,38%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,72%</t>
+          <t>88,77%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>13597</t>
+          <t>14005</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26795</t>
+          <t>27441</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>13886</t>
+          <t>13975</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>27742</t>
+          <t>27541</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>30675</t>
+          <t>30842</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>50054</t>
+          <t>49648</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>18,67%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>104107</t>
+          <t>103461</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>117305</t>
+          <t>116897</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>79,53%</t>
+          <t>79,04%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,61%</t>
+          <t>89,3%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>107343</t>
+          <t>107544</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>121199</t>
+          <t>121110</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>79,46%</t>
+          <t>79,61%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,72%</t>
+          <t>89,65%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>215933</t>
+          <t>216339</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>235312</t>
+          <t>235145</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>81,18%</t>
+          <t>81,33%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>88,47%</t>
+          <t>88,4%</t>
         </is>
       </c>
     </row>
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5812</t>
+          <t>5804</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>15315</t>
+          <t>15252</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>26,91%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5254</t>
+          <t>4882</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>15644</t>
+          <t>14896</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>12860</t>
+          <t>13377</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>26719</t>
+          <t>26257</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>21,58%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>41361</t>
+          <t>41424</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>50864</t>
+          <t>50872</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>72,98%</t>
+          <t>73,09%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>89,75%</t>
+          <t>89,76%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>49370</t>
+          <t>50118</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>59760</t>
+          <t>60132</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>75,94%</t>
+          <t>77,09%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>92,49%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>94971</t>
+          <t>95433</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>108830</t>
+          <t>108313</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>78,04%</t>
+          <t>78,42%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>89,43%</t>
+          <t>89,01%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>73616</t>
+          <t>74234</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>102829</t>
+          <t>101623</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>70178</t>
+          <t>71865</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>101803</t>
+          <t>100885</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>153613</t>
+          <t>152826</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>193312</t>
+          <t>192781</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>14,86%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>525152</t>
+          <t>526358</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>554365</t>
+          <t>553747</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>83,63%</t>
+          <t>83,82%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>88,28%</t>
+          <t>88,18%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>567913</t>
+          <t>568831</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>599538</t>
+          <t>597851</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>84,8%</t>
+          <t>84,94%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>89,52%</t>
+          <t>89,27%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1104385</t>
+          <t>1104916</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1144084</t>
+          <t>1144871</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>85,1%</t>
+          <t>85,14%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>88,16%</t>
+          <t>88,22%</t>
         </is>
       </c>
     </row>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7286</t>
+          <t>7083</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18476</t>
+          <t>18009</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8449</t>
+          <t>8513</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21716</t>
+          <t>23025</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>18381</t>
+          <t>18394</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>35022</t>
+          <t>36114</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8728,7 +8728,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>15,09%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>84784</t>
+          <t>85251</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>95974</t>
+          <t>96177</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>82,11%</t>
+          <t>82,56%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>93,14%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>114401</t>
+          <t>113092</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>127668</t>
+          <t>127604</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,05%</t>
+          <t>83,08%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>204355</t>
+          <t>203263</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>220996</t>
+          <t>220983</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,7 +8836,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,37%</t>
+          <t>84,91%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7876</t>
+          <t>8012</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19126</t>
+          <t>19214</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8840</t>
+          <t>8344</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21228</t>
+          <t>21225</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>19845</t>
+          <t>19271</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>36020</t>
+          <t>35782</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>19,04%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>75555</t>
+          <t>75467</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>86805</t>
+          <t>86669</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>79,8%</t>
+          <t>79,71%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,68%</t>
+          <t>91,54%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>72018</t>
+          <t>72021</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>84406</t>
+          <t>84902</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>77,23%</t>
+          <t>77,24%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,52%</t>
+          <t>91,05%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>151907</t>
+          <t>152145</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>168082</t>
+          <t>168656</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>80,83%</t>
+          <t>80,96%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>89,44%</t>
+          <t>89,75%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3203</t>
+          <t>3458</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10876</t>
+          <t>11379</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3077</t>
+          <t>3082</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14577</t>
+          <t>14150</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>22,41%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7746</t>
+          <t>7529</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>21512</t>
+          <t>21584</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>19,09%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>39049</t>
+          <t>38546</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>46722</t>
+          <t>46467</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>78,21%</t>
+          <t>77,21%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>93,07%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>48560</t>
+          <t>48987</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>60060</t>
+          <t>60055</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>76,91%</t>
+          <t>77,59%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>91550</t>
+          <t>91478</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>105316</t>
+          <t>105533</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>80,97%</t>
+          <t>80,91%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>93,34%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>24985</t>
+          <t>25332</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>121787</t>
+          <t>111113</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>56,92%</t>
+          <t>51,93%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>26147</t>
+          <t>25306</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>54751</t>
+          <t>51784</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>58255</t>
+          <t>59299</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>155143</t>
+          <t>169472</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>36,37%</t>
+          <t>39,73%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>92179</t>
+          <t>102853</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>188981</t>
+          <t>188634</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>43,08%</t>
+          <t>48,07%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,32%</t>
+          <t>88,16%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>157855</t>
+          <t>160822</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>186459</t>
+          <t>187300</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,25%</t>
+          <t>75,64%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,7%</t>
+          <t>88,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>271429</t>
+          <t>257100</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>368317</t>
+          <t>367273</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>63,63%</t>
+          <t>60,27%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,34%</t>
+          <t>86,1%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>17108</t>
+          <t>17460</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>35464</t>
+          <t>35699</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>30,22%</t>
+          <t>30,42%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>14349</t>
+          <t>14617</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>56779</t>
+          <t>63170</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>35,59%</t>
+          <t>39,6%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>36388</t>
+          <t>36771</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>81175</t>
+          <t>80319</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>29,32%</t>
+          <t>29,01%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>81878</t>
+          <t>81643</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>100234</t>
+          <t>99882</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>69,78%</t>
+          <t>69,58%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>85,42%</t>
+          <t>85,12%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>102761</t>
+          <t>96370</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>145191</t>
+          <t>144923</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>64,41%</t>
+          <t>60,4%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,01%</t>
+          <t>90,84%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>195706</t>
+          <t>196562</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>240493</t>
+          <t>240110</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>70,68%</t>
+          <t>70,99%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>86,86%</t>
+          <t>86,72%</t>
         </is>
       </c>
     </row>
@@ -10353,12 +10353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2280</t>
+          <t>2132</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9303</t>
+          <t>9734</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1906</t>
+          <t>2259</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11441</t>
+          <t>10978</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5792</t>
+          <t>5796</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>16845</t>
+          <t>17690</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10443,7 +10443,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,7%</t>
         </is>
       </c>
     </row>
@@ -10466,12 +10466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>59592</t>
+          <t>59161</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>66615</t>
+          <t>66763</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>86,5%</t>
+          <t>85,87%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>59013</t>
+          <t>59476</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>68548</t>
+          <t>68195</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>83,76%</t>
+          <t>84,42%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>122504</t>
+          <t>121659</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>133557</t>
+          <t>133553</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,7 +10551,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>87,91%</t>
+          <t>87,3%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>81275</t>
+          <t>83927</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>190321</t>
+          <t>190055</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>29,33%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>83306</t>
+          <t>82566</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>138880</t>
+          <t>137795</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>179830</t>
+          <t>178450</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>300741</t>
+          <t>305421</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>22,08%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>457747</t>
+          <t>458013</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>566793</t>
+          <t>564141</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>70,63%</t>
+          <t>70,67%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>87,46%</t>
+          <t>87,05%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>596220</t>
+          <t>597305</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>651794</t>
+          <t>652534</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>81,11%</t>
+          <t>81,25%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>88,67%</t>
+          <t>88,77%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1082427</t>
+          <t>1077747</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1203338</t>
+          <t>1204718</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>78,26%</t>
+          <t>77,92%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>87,0%</t>
+          <t>87,1%</t>
         </is>
       </c>
     </row>
